--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_11_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_11_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38115.19770566298</v>
+        <v>42734.23107227671</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8034137.820949661</v>
+        <v>8041589.773721423</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22317474.00149213</v>
+        <v>22317222.39794713</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4186618.537673994</v>
+        <v>4186078.493302924</v>
       </c>
     </row>
     <row r="11">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>218.5557354670911</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>233.8632089398365</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>228.2285498101873</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>227.2611138478472</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>228.0661862960586</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>229.4987093231087</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>136.7994484083213</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>137.1532948742138</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>140.4990339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>129.6634384984276</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>141.0609519916142</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>132.7421998671604</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.158075972814</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>134.0803811992711</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>138.0777675541624</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>126.8576920062168</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>137.6918827141379</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K11" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L11" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M11" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N11" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O11" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P11" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K12" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L12" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M12" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N12" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O12" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P12" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q12" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8825,25 +8825,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L13" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M13" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N13" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O13" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P13" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K14" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L14" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M14" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N14" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O14" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P14" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q14" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K15" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L15" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M15" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N15" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O15" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P15" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L16" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M16" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N16" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O16" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P16" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K17" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L17" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M17" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N17" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O17" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P17" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q17" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K18" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L18" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M18" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N18" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O18" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P18" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L19" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M19" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N19" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O19" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P19" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K20" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L20" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M20" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N20" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O20" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P20" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q20" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K21" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L21" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M21" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N21" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O21" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P21" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L22" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M22" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N22" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O22" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P22" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K23" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L23" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M23" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N23" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O23" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P23" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K24" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L24" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M24" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N24" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O24" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P24" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q24" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L25" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M25" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N25" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O25" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P25" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K26" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L26" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M26" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N26" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O26" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P26" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q26" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K27" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L27" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M27" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N27" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O27" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P27" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q27" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L28" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M28" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N28" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O28" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P28" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K29" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L29" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M29" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N29" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O29" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P29" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q29" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K30" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L30" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M30" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N30" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O30" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P30" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q30" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L31" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M31" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N31" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O31" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P31" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K32" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L32" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M32" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N32" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O32" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P32" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q32" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K33" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L33" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M33" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N33" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O33" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P33" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L34" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M34" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N34" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O34" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P34" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K35" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L35" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M35" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N35" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O35" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P35" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q35" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K36" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L36" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M36" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N36" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O36" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P36" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q36" t="n">
-        <v>94.67837785960643</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L37" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M37" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N37" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O37" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P37" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K38" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L38" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M38" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N38" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O38" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P38" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q38" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K39" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L39" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M39" t="n">
-        <v>52.20903392201834</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N39" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O39" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P39" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q39" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>94.44440571151897</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L40" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M40" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N40" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O40" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P40" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K41" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L41" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M41" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N41" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O41" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P41" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q41" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K42" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L42" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M42" t="n">
-        <v>52.20903392201834</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N42" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O42" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P42" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q42" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>94.44440571151897</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L43" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M43" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N43" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O43" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P43" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K44" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L44" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M44" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N44" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O44" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P44" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q44" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>93.3068247798742</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K45" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L45" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M45" t="n">
-        <v>52.20903392201834</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N45" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O45" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P45" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q45" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>94.44440571151897</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L46" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M46" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N46" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O46" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P46" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.2906772136275</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>339.3512895529531</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>210.0109347965366</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>10.92568633953715</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,19 +23023,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.688322330122702</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>149.1115350265769</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>208.7452454656423</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0430555942821</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3446880837159</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23072,16 +23072,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3370643330219</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>112.1731234817795</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>89.17446304009432</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1369403828616242</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,16 +23105,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>99.75719264320917</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>171.5633126132718</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1387192608593</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9409575526729</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9855695223932</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>162.1790741467838</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>155.2877864026681</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>92.97670470683673</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>21.64096723571893</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,22 +23178,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.067145653139306</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>85.70904325169438</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>177.0501454755301</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>223.9223193484477</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9224746741831</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3187342745236</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H11" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I11" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S11" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T11" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H12" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I12" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.12255113377519</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S12" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T12" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H13" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I13" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J13" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>61.24704325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R13" t="n">
-        <v>163.9148667870055</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S13" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T13" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H14" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I14" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S14" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T14" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H15" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I15" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S15" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T15" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H16" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I16" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J16" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R16" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S16" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T16" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H17" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I17" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S17" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T17" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H18" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I18" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S18" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T18" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H19" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I19" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J19" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R19" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S19" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T19" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H20" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I20" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S20" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T20" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H21" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I21" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S21" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T21" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H22" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I22" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J22" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R22" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S22" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T22" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H23" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I23" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S23" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T23" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H24" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I24" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S24" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T24" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H25" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I25" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J25" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R25" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S25" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T25" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H26" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I26" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S26" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T26" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H27" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I27" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S27" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T27" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H28" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I28" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J28" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R28" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S28" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T28" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H29" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I29" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S29" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T29" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H30" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I30" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S30" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T30" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H31" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I31" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J31" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R31" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S31" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T31" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H32" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I32" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S32" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T32" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H33" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I33" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S33" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T33" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H34" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I34" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J34" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R34" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S34" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T34" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H35" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I35" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S35" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T35" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H36" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I36" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S36" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T36" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H37" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I37" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J37" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R37" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S37" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T37" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H38" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I38" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S38" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T38" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H39" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I39" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S39" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T39" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H40" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I40" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J40" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R40" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S40" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T40" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H41" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I41" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S41" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T41" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H42" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I42" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S42" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T42" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H43" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I43" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J43" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R43" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S43" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T43" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H44" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I44" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S44" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T44" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H45" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I45" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S45" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T45" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H46" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I46" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J46" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R46" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S46" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T46" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>365778.421574131</v>
+        <v>365525.1788069177</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>360889.0090638404</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>360889.0090638403</v>
+        <v>360853.7542290912</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69879.81359544015</v>
+        <v>69879.81359544017</v>
       </c>
       <c r="C2" t="n">
-        <v>69879.81359544015</v>
+        <v>69879.81359544017</v>
       </c>
       <c r="D2" t="n">
-        <v>70024.59272003033</v>
+        <v>69879.81359544017</v>
       </c>
       <c r="E2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="F2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="G2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="H2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="I2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="J2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="K2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="L2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="M2" t="n">
-        <v>74293.56566529057</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="N2" t="n">
-        <v>74293.56566529055</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="O2" t="n">
-        <v>74293.56566529056</v>
+        <v>74308.35629741133</v>
       </c>
       <c r="P2" t="n">
-        <v>74293.56566529056</v>
+        <v>74308.35629741133</v>
       </c>
     </row>
     <row r="3">
@@ -26319,10 +26319,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2569.242</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>130151.286</v>
+        <v>133100.0000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59129.07304229552</v>
+        <v>58383.5376633838</v>
       </c>
       <c r="C4" t="n">
-        <v>59129.07304229552</v>
+        <v>58383.5376633838</v>
       </c>
       <c r="D4" t="n">
-        <v>58747.51503245945</v>
+        <v>58383.5376633838</v>
       </c>
       <c r="E4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="F4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="G4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="H4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="I4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="J4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="K4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="L4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="M4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="N4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="O4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
       <c r="P4" t="n">
-        <v>35140.29806987385</v>
+        <v>34598.38391202978</v>
       </c>
     </row>
     <row r="5">
@@ -26423,43 +26423,43 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33693</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="F5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="G5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="H5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="I5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="J5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="K5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="L5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="M5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="N5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="O5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="P5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-22131.32406794363</v>
       </c>
       <c r="C6" t="n">
-        <v>-22876.85944685536</v>
+        <v>-22131.32406794363</v>
       </c>
       <c r="D6" t="n">
-        <v>-24985.16431242912</v>
+        <v>-22131.32406794363</v>
       </c>
       <c r="E6" t="n">
-        <v>-94595.01840458329</v>
+        <v>-97001.63971962682</v>
       </c>
       <c r="F6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="G6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="H6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="I6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="J6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="K6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="L6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="M6" t="n">
-        <v>35556.26759541672</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="N6" t="n">
-        <v>35556.26759541669</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="O6" t="n">
-        <v>35556.26759541671</v>
+        <v>36098.36028037323</v>
       </c>
       <c r="P6" t="n">
-        <v>35556.26759541671</v>
+        <v>36098.36028037323</v>
       </c>
     </row>
   </sheetData>
@@ -26681,43 +26681,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="H3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="I3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="J3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="K3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="L3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="M3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="N3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="P3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
     </row>
     <row r="4">
@@ -26892,34 +26892,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26980,13 +26980,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01206030150753768</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1235125628140703</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4649547738693469</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.023603015075377</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.534115577889448</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.903206030150754</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.117683417085427</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.151949748743719</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.032025125628141</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.734286432160804</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.302376884422111</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7575829145728643</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2748241206030153</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05279396984924622</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009648241206030141</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006452830188679246</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06232075471698115</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2221698113207548</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6096509433962268</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.041990566037736</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.401084905660378</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.635</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.678273584905661</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.535292452830189</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.232207547169812</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8236981132075474</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4006415094339625</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1198584905660377</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02600943396226414</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0004245283018867927</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00540983606557377</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04809836065573773</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.162688524590164</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3824754098360656</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6285245901639342</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8042950819672132</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8480163934426227</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8278524590163939</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7646557377049182</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6542950819672128</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4530000000000001</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2432459016393443</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09427868852459013</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02311475409836065</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0002950819672131151</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6633165829145727</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H11" t="n">
-        <v>6.793190954773869</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I11" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J11" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K11" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L11" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M11" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N11" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O11" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P11" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q11" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R11" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S11" t="n">
-        <v>15.11532663316584</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T11" t="n">
-        <v>2.903668341708544</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05306532663316581</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3549056603773587</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H12" t="n">
-        <v>3.427641509433965</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I12" t="n">
-        <v>12.21933962264152</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J12" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K12" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L12" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M12" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N12" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O12" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P12" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.30339622641511</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R12" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S12" t="n">
-        <v>6.592216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T12" t="n">
-        <v>1.430518867924529</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02334905660377361</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2975409836065575</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H13" t="n">
-        <v>2.645409836065577</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I13" t="n">
-        <v>8.947868852459022</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J13" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K13" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L13" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M13" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N13" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O13" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P13" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.91500000000001</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R13" t="n">
-        <v>13.37852459016394</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S13" t="n">
-        <v>5.18532786885246</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T13" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01622950819672134</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H14" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I14" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J14" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K14" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L14" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M14" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N14" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O14" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P14" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q14" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R14" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S14" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T14" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H15" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I15" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J15" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K15" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L15" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M15" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N15" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O15" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P15" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R15" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S15" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T15" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H16" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I16" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J16" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K16" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L16" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M16" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N16" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O16" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P16" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q16" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R16" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S16" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T16" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H17" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I17" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J17" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K17" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L17" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M17" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N17" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O17" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P17" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q17" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R17" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S17" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T17" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U17" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H18" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I18" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J18" t="n">
-        <v>33.53080188679248</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K18" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L18" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M18" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N18" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O18" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P18" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R18" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S18" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T18" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U18" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H19" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I19" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J19" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K19" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L19" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M19" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N19" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O19" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P19" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R19" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S19" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T19" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H20" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I20" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J20" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K20" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L20" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M20" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N20" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O20" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P20" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q20" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R20" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S20" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T20" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H21" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I21" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J21" t="n">
-        <v>33.53080188679249</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K21" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L21" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M21" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N21" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O21" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P21" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q21" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R21" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S21" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T21" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U21" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H22" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I22" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J22" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K22" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L22" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M22" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N22" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O22" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P22" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R22" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S22" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T22" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H23" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I23" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J23" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K23" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L23" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M23" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N23" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O23" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P23" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q23" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R23" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S23" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T23" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U23" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H24" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I24" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J24" t="n">
-        <v>33.53080188679249</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K24" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L24" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M24" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N24" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O24" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P24" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q24" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R24" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S24" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T24" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U24" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H25" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I25" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J25" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K25" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L25" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M25" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N25" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O25" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P25" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q25" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R25" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S25" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T25" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H26" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I26" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J26" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K26" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L26" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M26" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N26" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O26" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P26" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q26" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R26" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S26" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T26" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U26" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H27" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I27" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J27" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K27" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L27" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M27" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N27" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O27" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P27" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R27" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S27" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T27" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U27" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H28" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I28" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J28" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K28" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L28" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M28" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N28" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O28" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P28" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R28" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S28" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T28" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H29" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I29" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J29" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K29" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L29" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M29" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N29" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O29" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P29" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q29" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R29" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S29" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T29" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U29" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H30" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I30" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J30" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K30" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L30" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M30" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N30" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O30" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P30" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q30" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R30" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S30" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T30" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U30" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H31" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I31" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J31" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K31" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L31" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M31" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N31" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O31" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P31" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R31" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S31" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T31" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H32" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I32" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J32" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K32" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L32" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M32" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N32" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O32" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P32" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q32" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R32" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S32" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T32" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U32" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H33" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I33" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J33" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K33" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L33" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M33" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N33" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O33" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P33" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q33" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R33" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S33" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T33" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H34" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I34" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J34" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K34" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L34" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M34" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N34" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O34" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P34" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q34" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R34" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S34" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T34" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H35" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I35" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J35" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K35" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L35" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M35" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N35" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O35" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P35" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q35" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R35" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S35" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T35" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U35" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H36" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I36" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J36" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K36" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L36" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M36" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N36" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O36" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P36" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q36" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R36" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S36" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T36" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U36" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H37" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I37" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J37" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K37" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L37" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M37" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N37" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O37" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P37" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R37" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S37" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T37" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H38" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I38" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J38" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K38" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L38" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M38" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N38" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O38" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P38" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q38" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R38" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S38" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T38" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U38" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H39" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I39" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J39" t="n">
-        <v>33.53080188679249</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K39" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L39" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M39" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N39" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O39" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P39" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q39" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R39" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S39" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T39" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U39" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H40" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I40" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J40" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K40" t="n">
-        <v>34.56885245901641</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L40" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M40" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N40" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O40" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P40" t="n">
-        <v>35.98622950819673</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q40" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R40" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S40" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T40" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U40" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H41" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I41" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J41" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K41" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L41" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M41" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N41" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O41" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P41" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q41" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R41" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S41" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T41" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U41" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H42" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I42" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J42" t="n">
-        <v>33.53080188679249</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K42" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L42" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M42" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N42" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O42" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P42" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q42" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R42" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S42" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T42" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U42" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H43" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I43" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J43" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K43" t="n">
-        <v>34.56885245901641</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L43" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M43" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N43" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O43" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P43" t="n">
-        <v>35.98622950819673</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q43" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R43" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S43" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T43" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H44" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I44" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J44" t="n">
-        <v>56.29816582914579</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K44" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L44" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M44" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N44" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O44" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P44" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q44" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R44" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S44" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T44" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U44" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H45" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I45" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J45" t="n">
-        <v>33.53080188679249</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K45" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L45" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M45" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N45" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O45" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P45" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q45" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R45" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S45" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T45" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U45" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H46" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I46" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J46" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K46" t="n">
-        <v>34.56885245901641</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L46" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M46" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N46" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O46" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P46" t="n">
-        <v>35.98622950819673</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R46" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S46" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T46" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
